--- a/system_development/BOM-V0.1.xlsx
+++ b/system_development/BOM-V0.1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ARTS (08222026)\Quantum sensing\Setup\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/06027168005bd3d0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{731F55EB-BF42-48BA-B2E2-DD97271EEBB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{731F55EB-BF42-48BA-B2E2-DD97271EEBB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{863D4CC4-5A39-4F3C-90F2-C9B914B25EC1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="179">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -561,6 +561,18 @@
   </si>
   <si>
     <t>Helmholtz coil system</t>
+  </si>
+  <si>
+    <t>Microwave isolator</t>
+  </si>
+  <si>
+    <t>T-2S63T-45</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/145853642058?_skw=Teledyne+Microwave+isolator&amp;itmmeta=01M4E5WS1WMYZE8F7R7MQBKRH8&amp;hash=item21f58df54a:g:5tcAAOSwSVZmex6Z&amp;itmprp=enc%3AAQALAAAA8GfYFPkwiKCW4ZNSs2u11xC%2FdJzFNDDIfQvetPIT8eE6i8bhpFSTn1BNMKTwHZ1hq9RkYXaTC%2FuG9z5lcJShcMaoIMUqtgK%2Fuzi4EbdY%2BXo%2BgX6b7K66Bxec05dvnG4XA0VWVg%2FgroI6uNgNr70ULsVr0USn0Cb55egnyNhxvWDp1TwaUn3eUNUeC01mj%2F5zIHB0ePzX9wdOEmTvpbWwIWQhfXSwbpWGOE309xbTh7yoLrO9qLulq2Xa58C9g0GTc6UP4cbOMIs7ZKVG%2BXLOCZeUDVoTtoVrUi8j0jxHVchaorD%2FDIUS7y0DUt7ZIVzD4Q%3D%3D%7Ctkp%3ABFBMjpHzxaNo</t>
+  </si>
+  <si>
+    <t>20dB Microwave Isolator,  2.5-5.0 GHz, SMA Female </t>
   </si>
 </sst>
 </file>
@@ -1070,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
@@ -2282,13 +2294,40 @@
       <c r="H42" s="4"/>
       <c r="I42" s="3"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="F43" s="7" t="s">
+    <row r="43" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>175</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="s">
+        <v>178</v>
+      </c>
+      <c r="D43" t="s">
+        <v>176</v>
+      </c>
+      <c r="E43" s="14">
+        <v>1</v>
+      </c>
+      <c r="F43" s="15">
+        <v>64.989999999999995</v>
+      </c>
+      <c r="G43" s="9">
+        <v>64.989999999999995</v>
+      </c>
+      <c r="H43" s="4"/>
+      <c r="I43" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F44" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G43" s="5">
-        <f>SUM(G2:G42)</f>
-        <v>34775.019999999997</v>
+      <c r="G44" s="5">
+        <f>SUM(G2:G43)</f>
+        <v>34840.009999999995</v>
       </c>
     </row>
   </sheetData>
